--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_381_R39.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_381_R39.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6241</v>
+        <v>7.3838</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7621</v>
+        <v>6.6511</v>
       </c>
       <c r="F2" t="n">
-        <v>0.862</v>
+        <v>0.7327</v>
       </c>
       <c r="G2" t="n">
         <v>4.447</v>
@@ -610,13 +610,13 @@
         <v>2.0473</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7328</v>
+        <v>0.0269</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6344</v>
+        <v>0.2545</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0983</v>
+        <v>-0.2276</v>
       </c>
       <c r="V2" t="n">
         <v>1.0901</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.883</v>
+        <v>4.9602</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3359</v>
+        <v>5.2192</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4529</v>
+        <v>-0.259</v>
       </c>
       <c r="G3" t="n">
         <v>2.8016</v>
@@ -688,13 +688,13 @@
         <v>1.1374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.146</v>
+        <v>-0.0688</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6586</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8046</v>
+        <v>-0.6107</v>
       </c>
       <c r="V3" t="n">
         <v>1.0901</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6832</v>
+        <v>3.382</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5369</v>
+        <v>1.6883</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8538</v>
+        <v>1.6938</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8349</v>
+        <v>-1.0131</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9308</v>
+        <v>-0.4823</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0959</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0437</v>
+        <v>0.152</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8947</v>
+        <v>0.8435</v>
       </c>
       <c r="L4" t="n">
-        <v>0.149</v>
+        <v>-0.6915</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2088</v>
+        <v>-1.1651</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9639</v>
+        <v>-1.3258</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2449</v>
+        <v>0.1608</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9099</v>
+        <v>1.8198</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1374</v>
+        <v>-0.2275</v>
       </c>
       <c r="R4" t="n">
         <v>2.0473</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6636</v>
+        <v>1.0985</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4722</v>
+        <v>0.6736</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1914</v>
+        <v>0.4249</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.7253</v>
+        <v>1.4768</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1583</v>
+        <v>1.0901</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.8836</v>
+        <v>0.3867</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3889</v>
+        <v>1.6478</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7275</v>
+        <v>1.1279</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6614</v>
+        <v>0.5198</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0131</v>
+        <v>0.4389</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4823</v>
+        <v>-0.225</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5306999999999999</v>
+        <v>0.6639</v>
       </c>
       <c r="J5" t="n">
-        <v>0.152</v>
+        <v>0.757</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8435</v>
+        <v>0.3432</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6915</v>
+        <v>0.4138</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1651</v>
+        <v>-0.3182</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3258</v>
+        <v>-0.5682</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1608</v>
+        <v>0.2501</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8198</v>
+        <v>0.6824</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2275</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0473</v>
+        <v>0.6824</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1054</v>
+        <v>0.3681</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2872</v>
+        <v>0.2126</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3925</v>
+        <v>0.1556</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4768</v>
+        <v>0.1583</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0901</v>
+        <v>0.1583</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.725</v>
+        <v>1.6089</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0112</v>
+        <v>3.6242</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7138</v>
+        <v>-2.0154</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4389</v>
+        <v>1.8349</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.225</v>
+        <v>1.9308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6639</v>
+        <v>-0.0959</v>
       </c>
       <c r="J6" t="n">
-        <v>0.757</v>
+        <v>3.0437</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3432</v>
+        <v>2.8947</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4138</v>
+        <v>0.149</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3182</v>
+        <v>-1.2088</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5682</v>
+        <v>-0.9639</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2501</v>
+        <v>-0.2449</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6824</v>
+        <v>0.9099</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6824</v>
+        <v>2.0473</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4453</v>
+        <v>1.5894</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0958</v>
+        <v>1.5595</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3495</v>
+        <v>0.0298</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1583</v>
+        <v>-2.7253</v>
       </c>
       <c r="W6" t="n">
         <v>0.1583</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.8836</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1047</v>
+        <v>-0.9243</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3485</v>
+        <v>-1.8604</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4532</v>
+        <v>0.9361</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6992</v>
@@ -1000,13 +1000,13 @@
         <v>0.9099</v>
       </c>
       <c r="S7" t="n">
-        <v>1.894</v>
+        <v>0.865</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2213</v>
+        <v>0.7095</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6727</v>
+        <v>0.1555</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.879</v>
+        <v>-1.7173</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1441</v>
+        <v>-1.3389</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2651</v>
+        <v>-0.3784</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2487</v>
+        <v>-3.4228</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.886</v>
+        <v>-1.7091</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6374</v>
+        <v>-1.7136</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5068</v>
+        <v>-2.0514</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.0778</v>
+        <v>0.1343</v>
       </c>
       <c r="L8" t="n">
-        <v>0.571</v>
+        <v>-2.1857</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7419</v>
+        <v>-1.3713</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8083</v>
+        <v>-1.8434</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0664</v>
+        <v>0.4721</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6824</v>
+        <v>2.2747</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5022</v>
+        <v>-0.2275</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8198</v>
+        <v>2.5022</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5971</v>
+        <v>0.5208</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7066</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8905999999999999</v>
+        <v>-0.4192</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5451</v>
+        <v>-1.0901</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7034</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4751</v>
+        <v>-2.0784</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6442</v>
+        <v>-3.1172</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8309</v>
+        <v>1.0388</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4228</v>
+        <v>-2.2487</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7091</v>
+        <v>-2.886</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7136</v>
+        <v>0.6374</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0514</v>
+        <v>-1.5068</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1343</v>
+        <v>-2.0778</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1857</v>
+        <v>0.571</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3713</v>
+        <v>-0.7419</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8434</v>
+        <v>-0.8083</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4721</v>
+        <v>0.0664</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2747</v>
+        <v>-0.6824</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2275</v>
+        <v>-2.5022</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5022</v>
+        <v>1.8198</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.237</v>
+        <v>1.3978</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6347</v>
+        <v>0.7335</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8717</v>
+        <v>0.6643</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0901</v>
+        <v>-0.5451</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0901</v>
+        <v>-0.7034</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LESSORT</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0878</v>
+        <v>-2.2801</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7173</v>
+        <v>-0.3603</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3705</v>
+        <v>-1.9198</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2139</v>
+        <v>0.1009</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2246</v>
+        <v>1.7253</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0107</v>
+        <v>-1.6243</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7489</v>
+        <v>0.4809</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6371</v>
+        <v>2.3272</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1118</v>
+        <v>-1.8464</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.535</v>
+        <v>-0.38</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4126</v>
+        <v>-0.602</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1225</v>
+        <v>0.222</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8198</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2747</v>
+        <v>-1.3648</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4549</v>
+        <v>1.1374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3017</v>
+        <v>-0.1317</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1915</v>
+        <v>0.3653</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1102</v>
+        <v>-0.497</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1802</v>
+        <v>-2.0219</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X10" t="n">
         <v>-2.1802</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>M. LESSORT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4079</v>
+        <v>-2.7053</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1326</v>
+        <v>-0.5288</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2753</v>
+        <v>-2.1766</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1009</v>
+        <v>1.2139</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7253</v>
+        <v>1.2246</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6243</v>
+        <v>-0.0107</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4809</v>
+        <v>1.7489</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3272</v>
+        <v>1.6371</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8464</v>
+        <v>0.1118</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.38</v>
+        <v>-0.535</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.602</v>
+        <v>-0.4126</v>
       </c>
       <c r="O11" t="n">
-        <v>0.222</v>
+        <v>-0.1225</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2275</v>
+        <v>-1.8198</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3648</v>
+        <v>-2.2747</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1374</v>
+        <v>0.4549</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2595</v>
+        <v>0.0808</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.407</v>
+        <v>-0.0029</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8525</v>
+        <v>0.0837</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.0219</v>
+        <v>-2.1802</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>-2.1802</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.559100000000001</v>
+        <v>9.277300000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>10.3869</v>
+        <v>11.1051</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.827900000000001</v>
+        <v>-1.828</v>
       </c>
       <c r="G12" t="n">
-        <v>1.453399999999999</v>
+        <v>1.4534</v>
       </c>
       <c r="H12" t="n">
         <v>3.0101</v>
@@ -1363,7 +1363,7 @@
         <v>-1.5564</v>
       </c>
       <c r="J12" t="n">
-        <v>9.175500000000001</v>
+        <v>9.1755</v>
       </c>
       <c r="K12" t="n">
         <v>11.7019</v>
@@ -1372,7 +1372,7 @@
         <v>-2.5264</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.722199999999999</v>
+        <v>-7.7222</v>
       </c>
       <c r="N12" t="n">
         <v>-8.692</v>
@@ -1381,22 +1381,22 @@
         <v>0.97</v>
       </c>
       <c r="P12" t="n">
-        <v>6.824200000000001</v>
+        <v>6.824200000000002</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.961600000000001</v>
+        <v>-7.9616</v>
       </c>
       <c r="R12" t="n">
         <v>14.7859</v>
       </c>
       <c r="S12" t="n">
-        <v>5.0284</v>
+        <v>5.746799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>5.2691</v>
+        <v>5.9874</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2406000000000001</v>
+        <v>-0.2407</v>
       </c>
       <c r="V12" t="n">
         <v>-4.7473</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5718</v>
+        <v>4.1142</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1284</v>
+        <v>5.5189</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4435</v>
+        <v>-1.4047</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2342</v>
+        <v>8.4718</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5333</v>
+        <v>2.5594</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7675</v>
+        <v>5.9125</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2479</v>
+        <v>9.9176</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1362</v>
+        <v>4.7272</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1118</v>
+        <v>5.1903</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0137</v>
+        <v>-1.4457</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6695</v>
+        <v>-2.1679</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6558</v>
+        <v>0.7221</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6824</v>
+        <v>-4.0945</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-5.6868</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6824</v>
+        <v>1.5923</v>
       </c>
       <c r="S13" t="n">
-        <v>1.475</v>
+        <v>-0.8082</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7003</v>
+        <v>-0.347</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2252</v>
+        <v>-0.4612</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1802</v>
+        <v>0.5451</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1802</v>
+        <v>1.6352</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0953</v>
+        <v>3.3273</v>
       </c>
       <c r="E14" t="n">
-        <v>4.585</v>
+        <v>3.0778</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4898</v>
+        <v>0.2495</v>
       </c>
       <c r="G14" t="n">
-        <v>8.4718</v>
+        <v>0.2342</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5594</v>
+        <v>-0.5333</v>
       </c>
       <c r="I14" t="n">
-        <v>5.9125</v>
+        <v>0.7675</v>
       </c>
       <c r="J14" t="n">
-        <v>9.9176</v>
+        <v>0.2479</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7272</v>
+        <v>0.1362</v>
       </c>
       <c r="L14" t="n">
-        <v>5.1903</v>
+        <v>0.1118</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4457</v>
+        <v>-0.0137</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.1679</v>
+        <v>-0.6695</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7221</v>
+        <v>0.6558</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.0945</v>
+        <v>0.6824</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.6868</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5923</v>
+        <v>0.6824</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8271</v>
+        <v>0.2305</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2809</v>
+        <v>0.6496</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5462</v>
+        <v>-0.4192</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5451</v>
+        <v>2.1802</v>
       </c>
       <c r="W14" t="n">
-        <v>1.6352</v>
+        <v>2.1802</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1149</v>
+        <v>0.4902</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9478</v>
+        <v>0.5976</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.833</v>
+        <v>-0.1075</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1899</v>
@@ -1624,13 +1624,13 @@
         <v>0.9099</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5579</v>
+        <v>-0.1826</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1318</v>
+        <v>-0.2184</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6897</v>
+        <v>0.0358</v>
       </c>
       <c r="V15" t="n">
         <v>1.0901</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BEGARIN</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0806</v>
+        <v>0.3362</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7137</v>
+        <v>1.2319</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6332</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6474</v>
+        <v>-0.1846</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2617</v>
+        <v>1.1233</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9091</v>
+        <v>-1.3079</v>
       </c>
       <c r="J16" t="n">
-        <v>1.079</v>
+        <v>0.9198</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7432</v>
+        <v>2.3272</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.6642</v>
+        <v>-1.4075</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7264</v>
+        <v>-1.1044</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4815</v>
+        <v>-1.204</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2449</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6824</v>
+        <v>0.2275</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4549</v>
+        <v>1.3648</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4104</v>
+        <v>-0.4101</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7721</v>
+        <v>-0.3441</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3617</v>
+        <v>-0.066</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.7034</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7935</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.111</v>
+        <v>-0.5119</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3486</v>
+        <v>1.147</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4596</v>
+        <v>-1.6589</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1846</v>
+        <v>0.2568</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1233</v>
+        <v>-0.8608</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3079</v>
+        <v>1.1176</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9198</v>
+        <v>1.1612</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3272</v>
+        <v>0.5157</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4075</v>
+        <v>0.6455</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1044</v>
+        <v>-0.9044</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.204</v>
+        <v>-1.3765</v>
       </c>
       <c r="O17" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.4721</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2275</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3648</v>
+        <v>0.9099</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8572</v>
+        <v>-0.2245</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2273</v>
+        <v>0.0331</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6299</v>
+        <v>-0.2576</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7034</v>
+        <v>-0.3167</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7935</v>
+        <v>1.0901</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0901</v>
+        <v>-1.4068</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>J. BEGARIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2308</v>
+        <v>-0.9886</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0303</v>
+        <v>0.7799</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2611</v>
+        <v>-1.7684</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2568</v>
+        <v>-0.6474</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8608</v>
+        <v>1.2617</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1176</v>
+        <v>-1.9091</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1612</v>
+        <v>1.079</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5157</v>
+        <v>2.7432</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6455</v>
+        <v>-1.6642</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9044</v>
+        <v>-1.7264</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3765</v>
+        <v>-1.4815</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4721</v>
+        <v>-0.2449</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2275</v>
+        <v>-0.6824</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9099</v>
+        <v>0.4549</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9434</v>
+        <v>0.3412</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0837</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8598</v>
+        <v>-0.497</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3167</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0901</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.3952</v>
+        <v>-4.5002</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.0486</v>
+        <v>-4.4649</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3466</v>
+        <v>-0.0353</v>
       </c>
       <c r="G19" t="n">
         <v>-3.5274</v>
@@ -1936,13 +1936,13 @@
         <v>1.5923</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.3227</v>
+        <v>-1.4277</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2091</v>
+        <v>-0.6254</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1137</v>
+        <v>-0.8024</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-9.6846</v>
+        <v>-8.4915</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.8773</v>
+        <v>-6.0602</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8072</v>
+        <v>-2.4313</v>
       </c>
       <c r="G20" t="n">
         <v>-5.8669</v>
@@ -2014,13 +2014,13 @@
         <v>0.4549</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4056</v>
+        <v>-0.2125</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5626</v>
+        <v>0.2545</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.843</v>
+        <v>-0.467</v>
       </c>
       <c r="V20" t="n">
         <v>0.5451</v>
@@ -2047,22 +2047,22 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.558999999999997</v>
+        <v>-6.224300000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8279</v>
+        <v>1.827999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.387</v>
+        <v>-8.052299999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.453400000000001</v>
+        <v>-1.4534</v>
       </c>
       <c r="H21" t="n">
         <v>-3.0098</v>
       </c>
       <c r="I21" t="n">
-        <v>1.556499999999999</v>
+        <v>1.5565</v>
       </c>
       <c r="J21" t="n">
         <v>7.722299999999999</v>
@@ -2071,7 +2071,7 @@
         <v>8.692</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9699</v>
+        <v>-0.9699000000000004</v>
       </c>
       <c r="M21" t="n">
         <v>-9.175599999999999</v>
@@ -2092,13 +2092,13 @@
         <v>7.9614</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.0285</v>
+        <v>-2.6939</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2405999999999997</v>
+        <v>0.2404999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.2692</v>
+        <v>-2.9346</v>
       </c>
       <c r="V21" t="n">
         <v>4.7472</v>
